--- a/JP_60_Films_Watchlist.xlsx
+++ b/JP_60_Films_Watchlist.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'60 Films'!$A$1:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'60 Films'!$A$1:$I$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,13 +29,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -47,11 +40,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,20 +65,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
-        <bgColor rgb="00FCE5CD"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-        <bgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,29 +99,28 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -491,19 +483,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -521,7 +515,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Most Popular Film (Letterboxd)</t>
+          <t>Most Popular Film (all confirmed Watched)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -531,12 +525,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Recommended Film (not yet watched)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Letterboxd Link</t>
+          <t>Rec. Year</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Also on Retro list?</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
@@ -554,7 +558,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Forrest Gump</t>
         </is>
@@ -564,14 +568,18 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/forrest-gump/</t>
-        </is>
-      </c>
+          <t>The Terminal</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -587,7 +595,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Top Gun: Maverick</t>
         </is>
@@ -597,14 +605,18 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/top-gun-maverick/</t>
-        </is>
-      </c>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -620,7 +632,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Inception</t>
         </is>
@@ -630,14 +642,18 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/inception/</t>
-        </is>
-      </c>
+          <t>The Basketball Diaries</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -653,7 +669,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Fight Club</t>
         </is>
@@ -663,14 +679,18 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/fight-club/</t>
-        </is>
-      </c>
+          <t>Thelma &amp; Louise</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -686,7 +706,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Pirates of the Caribbean: The Curse of the Black Pearl</t>
         </is>
@@ -696,14 +716,18 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/pirates-of-the-caribbean-the-curse-of-the-black-pearl/</t>
-        </is>
-      </c>
+          <t>Corpse Bride</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -719,7 +743,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Suicide Squad</t>
         </is>
@@ -729,14 +753,18 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/suicide-squad-2016/</t>
-        </is>
-      </c>
+          <t>Spies in Disguise</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -752,7 +780,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Gladiator II</t>
         </is>
@@ -760,16 +788,20 @@
       <c r="E8" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/gladiator-ii/</t>
-        </is>
-      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Malcolm X</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -785,7 +817,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Oppenheimer</t>
         </is>
@@ -795,14 +827,18 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/oppenheimer-2023/</t>
-        </is>
-      </c>
+          <t>A Scanner Darkly</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -818,7 +854,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Zootopia 2</t>
         </is>
@@ -826,16 +862,20 @@
       <c r="E10" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/zootopia-2/</t>
-        </is>
-      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Get Smart</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -851,7 +891,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Deadpool &amp; Wolverine</t>
         </is>
@@ -859,16 +899,20 @@
       <c r="E11" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/deadpool-wolverine/</t>
-        </is>
-      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Adventureland</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -884,7 +928,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Avengers: Infinity War</t>
         </is>
@@ -894,14 +938,18 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/avengers-infinity-war/</t>
-        </is>
-      </c>
+          <t>Spiderhead</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -917,7 +965,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Knives Out</t>
         </is>
@@ -927,14 +975,18 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/knives-out-2019/</t>
-        </is>
-      </c>
+          <t>Gifted</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -950,7 +1002,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Interstellar</t>
         </is>
@@ -960,14 +1012,18 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/interstellar/</t>
-        </is>
-      </c>
+          <t>Spirit: Stallion of the Cimarron</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2002</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -983,7 +1039,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>The Dark Knight</t>
         </is>
@@ -993,14 +1049,18 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-dark-knight/</t>
-        </is>
-      </c>
+          <t>Vice</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1016,24 +1076,28 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Prisoners</t>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Deadpool &amp; Wolverine</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/prisoners/</t>
-        </is>
-      </c>
+          <t>Flushed Away</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1049,7 +1113,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>The Matrix</t>
         </is>
@@ -1059,14 +1123,18 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-matrix/</t>
-        </is>
-      </c>
+          <t>Point Break</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1082,7 +1150,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Pulp Fiction</t>
         </is>
@@ -1090,16 +1158,20 @@
       <c r="E18" s="2" t="n">
         <v>1994</v>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/pulp-fiction/</t>
-        </is>
-      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Do the Right Thing</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1989</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1115,7 +1187,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>The Shawshank Redemption</t>
         </is>
@@ -1125,14 +1197,18 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-shawshank-redemption/</t>
-        </is>
-      </c>
+          <t>The Bucket List</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1148,7 +1224,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Fantastic Mr. Fox</t>
         </is>
@@ -1156,16 +1232,20 @@
       <c r="E20" s="2" t="n">
         <v>2009</v>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/fantastic-mr-fox/</t>
-        </is>
-      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>O Brother, Where Art Thou?</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1181,7 +1261,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Gladiator</t>
         </is>
@@ -1191,14 +1271,18 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/gladiator-2000/</t>
-        </is>
-      </c>
+          <t>Master and Commander: The Far Side of the World</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1214,7 +1298,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Glass Onion</t>
         </is>
@@ -1224,14 +1308,18 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/glass-onion/</t>
-        </is>
-      </c>
+          <t>The Adventures of Tintin</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1247,7 +1335,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Snatch</t>
         </is>
@@ -1257,14 +1345,18 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/snatch/</t>
-        </is>
-      </c>
+          <t>Spy</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1280,7 +1372,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>The Departed</t>
         </is>
@@ -1290,14 +1382,18 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-departed/</t>
-        </is>
-      </c>
+          <t>The Lovely Bones</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1313,7 +1409,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Good Will Hunting</t>
         </is>
@@ -1323,14 +1419,18 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/good-will-hunting/</t>
-        </is>
-      </c>
+          <t>He's Just Not That Into You</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1346,7 +1446,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Joker</t>
         </is>
@@ -1356,14 +1456,18 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/joker-2019/</t>
-        </is>
-      </c>
+          <t>The Master</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1379,7 +1483,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Batman Begins</t>
         </is>
@@ -1389,14 +1493,18 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/batman-begins/</t>
-        </is>
-      </c>
+          <t>The Wind That Shakes the Barley</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1412,7 +1520,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Dune</t>
         </is>
@@ -1420,16 +1528,20 @@
       <c r="E28" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/dune-2021/</t>
-        </is>
-      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>The French Dispatch</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1445,7 +1557,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Barbie</t>
         </is>
@@ -1453,16 +1565,20 @@
       <c r="E29" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/barbie/</t>
-        </is>
-      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Blue Valentine</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1478,7 +1594,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Donnie Darko</t>
         </is>
@@ -1488,14 +1604,18 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/donnie-darko/</t>
-        </is>
-      </c>
+          <t>Brothers</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -1511,7 +1631,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Thor: Ragnarok</t>
         </is>
@@ -1521,14 +1641,18 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/thor-ragnarok/</t>
-        </is>
-      </c>
+          <t>A House of Dynamite</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -1544,7 +1668,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Spider-Man: No Way Home</t>
         </is>
@@ -1554,14 +1678,18 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/spider-man-no-way-home/</t>
-        </is>
-      </c>
+          <t>Rio</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -1577,7 +1705,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Sinners</t>
         </is>
@@ -1585,16 +1713,20 @@
       <c r="E33" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/sinners-2025/</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Just Mercy</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -1610,7 +1742,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Uncut Gems</t>
         </is>
@@ -1620,14 +1752,18 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/uncut-gems/</t>
-        </is>
-      </c>
+          <t>Grown Ups 2</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -1643,7 +1779,7 @@
           <t>Actor</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>The Truman Show</t>
         </is>
@@ -1653,14 +1789,18 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-truman-show/</t>
-        </is>
-      </c>
+          <t>A Christmas Carol</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -1676,7 +1816,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Notting Hill</t>
         </is>
@@ -1684,16 +1824,20 @@
       <c r="E36" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>Watched (also on Retro list)</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/notting-hill/</t>
-        </is>
-      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Wonder</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -1709,7 +1853,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Project Hail Mary</t>
         </is>
@@ -1717,16 +1861,20 @@
       <c r="E37" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/project-hail-mary/</t>
-        </is>
-      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Hoppers</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -1742,24 +1890,28 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Her</t>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Avengers: Infinity War</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/her/</t>
-        </is>
-      </c>
+          <t>The SpongeBob SquarePants Movie</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -1775,7 +1927,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Girl, Interrupted</t>
         </is>
@@ -1783,16 +1935,20 @@
       <c r="E39" s="2" t="n">
         <v>1999</v>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>Watched (also on Retro list)</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/girl-interrupted/</t>
-        </is>
-      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Kung Fu Panda 3</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -1808,7 +1964,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Bullet Train</t>
         </is>
@@ -1818,14 +1974,18 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/bullet-train/</t>
-        </is>
-      </c>
+          <t>The Prince of Egypt</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -1841,7 +2001,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>The Hunger Games</t>
         </is>
@@ -1851,14 +2011,18 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-hunger-games/</t>
-        </is>
-      </c>
+          <t>Causeway</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -1874,7 +2038,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>La La Land</t>
         </is>
@@ -1884,14 +2048,18 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/la-la-land/</t>
-        </is>
-      </c>
+          <t>The Favourite</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -1907,24 +2075,28 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>The Wolf of Wall Street</t>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Barbie</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-wolf-of-wall-street/</t>
-        </is>
-      </c>
+          <t>A Big Bold Beautiful Journey</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -1940,7 +2112,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Eyes Wide Shut</t>
         </is>
@@ -1950,14 +2122,18 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/eyes-wide-shut/</t>
-        </is>
-      </c>
+          <t>The Killing of a Sacred Deer</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -1973,7 +2149,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>The Lord of the Rings: The Fellowship of the Ring</t>
         </is>
@@ -1981,16 +2157,20 @@
       <c r="E45" s="2" t="n">
         <v>2001</v>
       </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-lord-of-the-rings-the-fellowship-of-the-ring/</t>
-        </is>
-      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Carol</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -2006,7 +2186,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Mad Max: Fury Road</t>
         </is>
@@ -2016,14 +2196,18 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/mad-max-fury-road/</t>
-        </is>
-      </c>
+          <t>The Road</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -2039,7 +2223,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Black Swan</t>
         </is>
@@ -2049,14 +2233,18 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/black-swan/</t>
-        </is>
-      </c>
+          <t>The Darjeeling Limited</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -2072,7 +2260,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>The Devil Wears Prada</t>
         </is>
@@ -2080,16 +2268,20 @@
       <c r="E48" s="2" t="n">
         <v>2006</v>
       </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>Watched (also on Retro list)</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-devil-wears-prada/</t>
-        </is>
-      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>The Idea of You</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -2105,7 +2297,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>American Psycho</t>
         </is>
@@ -2115,14 +2307,18 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/american-psycho/</t>
-        </is>
-      </c>
+          <t>Legally Blonde</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>2001</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2138,7 +2334,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Dune: Part Two</t>
         </is>
@@ -2146,16 +2342,20 @@
       <c r="E50" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/dune-part-two/</t>
-        </is>
-      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Malcolm &amp; Marie</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -2171,7 +2371,7 @@
           <t>Actress</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>The Perks of Being a Wallflower</t>
         </is>
@@ -2179,16 +2379,20 @@
       <c r="E51" s="2" t="n">
         <v>2012</v>
       </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-perks-of-being-a-wallflower/</t>
-        </is>
-      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>My Week with Marilyn</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2204,22 +2408,30 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Memento</t>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Interstellar</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2000</v>
+        <v>2014</v>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/memento/</t>
+          <t>Larceny</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>1996</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>You've watched every Nolan feature (incl. early shorts Following/Doodlebug/Tarantella) - only a 3-min 1996 student short remains</t>
         </is>
       </c>
     </row>
@@ -2237,24 +2449,28 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Jurassic Park</t>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Catch Me If You Can</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1993</v>
+        <v>2002</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/jurassic-park/</t>
-        </is>
-      </c>
+          <t>The Fabelmans</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2270,24 +2486,28 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Taxi Driver</t>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>The Wolf of Wall Street</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1976</v>
+        <v>2013</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/taxi-driver/</t>
-        </is>
-      </c>
+          <t>After Hours</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -2303,24 +2523,28 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Kill Bill: Vol. 1</t>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Pulp Fiction</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2003</v>
+        <v>1994</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/kill-bill-vol-1/</t>
-        </is>
-      </c>
+          <t>Four Rooms</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1995</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -2336,22 +2560,30 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Avatar</t>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Titanic</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2009</v>
+        <v>1997</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/avatar/</t>
+          <t>Piranha II: The Spawning</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1982</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>His directorial debut - schlocky B-movie, nothing like his later work</t>
         </is>
       </c>
     </row>
@@ -2369,24 +2601,28 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Arrival</t>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Dune</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="F57" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/arrival-2016/</t>
-        </is>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Polytechnique</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -2402,24 +2638,28 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Lady Bird</t>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Barbie</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/lady-bird/</t>
-        </is>
-      </c>
+          <t>Nights and Weekends</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -2435,22 +2675,30 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>The Lord of the Rings: The Return of the King</t>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>The Lord of the Rings: The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>Watched</t>
-        </is>
-      </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-lord-of-the-rings-the-return-of-the-king/</t>
+        <v>2001</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Braindead</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1992</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>aka Dead Alive</t>
         </is>
       </c>
     </row>
@@ -2468,24 +2716,28 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>The Social Network</t>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Fight Club</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2010</v>
+        <v>1999</v>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/the-social-network/</t>
-        </is>
-      </c>
+          <t>Mank</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -2501,88 +2753,152 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Alien</t>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Gladiator</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>1979</v>
+        <v>2000</v>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Recommended</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>https://letterboxd.com/film/alien/</t>
-        </is>
-      </c>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1985</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G61"/>
+  <autoFilter ref="A1:I61"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2594,83 +2910,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Total people</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Actors/Actresses</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="8" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Directors</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="8" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Already watched</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>17</v>
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Their 'most popular' film you'd already watched</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>...of which also on Retro list</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>3</v>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Recommended (genuinely unwatched) films found</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Recommended (not yet seen)</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>43</v>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>...of which also sitting on your Retro list</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Special case</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Christopher Nolan: every feature watched (incl. shorts) - only a 1996 student short remains</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/JP_60_Films_Watchlist.xlsx
+++ b/JP_60_Films_Watchlist.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="60 Films" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shows - Unwatched Seasons" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'60 Films'!$A$1:$I$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Shows - Unwatched Seasons'!$A$1:$G$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,7 +52,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +75,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE5CD"/>
+        <bgColor rgb="00FCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -118,6 +132,15 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2910,7 +2933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3001,7 +3024,329 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Shows with unwatched/abandoned seasons</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Total unwatched/abandoned episodes across shows</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Total unwatched/abandoned runtime across shows</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>245h 42m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Show Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Season(s)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Episodes</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total Runtime</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Ted Lasso</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Unwatched</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>7h 35m</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Currently airing weekly (finishes 7 Oct 2026) - eps 1-6 aired/runtime known, eps 7-10 runtime estimated from season average</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Lanterns</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ongoing</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Unwatched</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>7h 56m</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>New show, not yet started</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>The Sopranos</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>S1-S6 (all)</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Unwatched</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>83h 26m</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Not started at all - the only show on your list with zero seasons logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>The Walking Dead</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>S8-S11</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Abandoned</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>81h 34m</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Marked abandoned after S7 - seasons 1-7 watched</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Lost</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>S4-S6</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Abandoned</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49h 00m</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Marked abandoned after S3 - seasons 1-3 watched</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Westworld</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>S3-S4</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Abandoned</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16h 11m</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Marked abandoned after S2 - seasons 1-2 watched</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>247</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>245h 42m</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>